--- a/output/full_scan/batch_seq1_2026-07-14.xlsx
+++ b/output/full_scan/batch_seq1_2026-07-14.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O130"/>
+  <dimension ref="A1:O133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -898,21 +898,21 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1210</v>
+        <v>1515</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>684.1098602000085</v>
+        <v>700.4881626126539</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>57.1</v>
+        <v>41</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>57.80656439808028</v>
+        <v>72.06719501744513</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>40.16384856202693</v>
+        <v>53.20143938811633</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.6301986067934983</v>
+        <v>0.4645088219284881</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.0427131717975395</v>
+        <v>0.6461905246577393</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1540</v>
+        <v>1210</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>喬福</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>671.9974281197103</v>
+        <v>684.1098602000085</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>23</v>
+        <v>57.1</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>61.23497317969408</v>
+        <v>57.80656439808028</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>17.81798144612634</v>
+        <v>40.16384856202693</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.879821961072188</v>
+        <v>0.6301986067934983</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.0523480312459601</v>
+        <v>0.0427131717975395</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1216</v>
+        <v>1540</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>喬福</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>658.2953564208781</v>
+        <v>671.9974281197103</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>78.5</v>
+        <v>23</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>66.50106484820108</v>
+        <v>61.23497317969408</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>33.42745746588636</v>
+        <v>17.81798144612634</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.12499690455148</v>
+        <v>1.879821961072188</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.2642751954128151</v>
+        <v>0.0523480312459601</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1434</v>
+        <v>1216</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>福懋</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>635.4422001357775</v>
+        <v>658.2953564208781</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>18.3</v>
+        <v>78.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>60.82044067723644</v>
+        <v>66.50106484820108</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>31.20432140814041</v>
+        <v>33.42745746588636</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.9329478723817736</v>
+        <v>1.12499690455148</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.0612683709463417</v>
+        <v>0.2642751954128151</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1466</v>
+        <v>1447</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>633.1469518642535</v>
+        <v>646.5386992886682</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>18.5</v>
+        <v>8.07</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>65.07135151487671</v>
+        <v>57.3581120862565</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>26.04816289460926</v>
+        <v>43.55305910312518</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.114695186425349</v>
+        <v>0.4074518856737383</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.2370713508779111</v>
+        <v>0.027130046279267</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1468</v>
+        <v>1434</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>昶和</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>622.0631535332423</v>
+        <v>635.4422001357775</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>13.35</v>
+        <v>18.3</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>79.2984239945884</v>
+        <v>60.82044067723644</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>20.07431323939576</v>
+        <v>31.20432140814041</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.172948965124984</v>
+        <v>0.9329478723817736</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.1006941173799083</v>
+        <v>0.0612683709463417</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1444</v>
+        <v>1466</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>618.0352213706273</v>
+        <v>633.1469518642535</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>8.07</v>
+        <v>18.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>52.40982838952388</v>
+        <v>65.07135151487671</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>38.00650023441921</v>
+        <v>26.04816289460926</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.4266705779320119</v>
+        <v>2.114695186425349</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.0964878416605453</v>
+        <v>0.2370713508779111</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1452</v>
+        <v>1468</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>昶和</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>616.2289367056948</v>
+        <v>622.0631535332423</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>11.75</v>
+        <v>13.35</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>64.03238225920238</v>
+        <v>79.2984239945884</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>21.27295946084196</v>
+        <v>20.07431323939576</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.7365233145653617</v>
+        <v>1.172948965124984</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.0613922453272871</v>
+        <v>0.1006941173799083</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1465</v>
+        <v>1444</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>577.238639240771</v>
+        <v>618.0352213706273</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>12.9</v>
+        <v>8.07</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>54.08780266869378</v>
+        <v>52.40982838952388</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>25.6015157146539</v>
+        <v>38.00650023441921</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.5102485988831168</v>
+        <v>0.4266705779320119</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.009919164407616501</v>
+        <v>-0.0964878416605453</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1409</v>
+        <v>1452</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>宏益</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>569.9225218713934</v>
+        <v>616.2289367056948</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>26.4</v>
+        <v>11.75</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>50.02437645169209</v>
+        <v>64.03238225920238</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>22.77861621484296</v>
+        <v>21.27295946084196</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.699223558001385</v>
+        <v>0.7365233145653617</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.4684394201831747</v>
+        <v>0.0613922453272871</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1315</v>
+        <v>1435</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>548.3403160388941</v>
+        <v>605.1371082659631</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>63.8</v>
+        <v>26.55</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>62.86762610120188</v>
+        <v>56.93475442504826</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>21.93083511432705</v>
+        <v>17.58859686262652</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.751857089968651</v>
+        <v>0.2277867151616889</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.1276476302589928</v>
+        <v>0.2040771363771858</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1568</v>
+        <v>1465</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>倉佑</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>547.2071697627046</v>
+        <v>577.238639240771</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>31.1</v>
+        <v>12.9</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>35.13830303620269</v>
+        <v>54.08780266869378</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>22.8002054876211</v>
+        <v>25.6015157146539</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2.519628663635899</v>
+        <v>0.5102485988831168</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-1.203468713761227</v>
+        <v>-0.009919164407616501</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1531</v>
+        <v>1409</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>高林股</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>542.1971516837867</v>
+        <v>569.9225218713934</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>13</v>
+        <v>26.4</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>54.65174099939487</v>
+        <v>50.02437645169209</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>20.13290913310757</v>
+        <v>22.77861621484296</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.7468886081133818</v>
+        <v>0.699223558001385</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.0008761553814446</v>
+        <v>-0.4684394201831747</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1527</v>
+        <v>1315</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>532.3415729757384</v>
+        <v>548.3403160388941</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>33.95</v>
+        <v>63.8</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>58.64366926449721</v>
+        <v>62.86762610120188</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>21.16061625223304</v>
+        <v>21.93083511432705</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.281909330394413</v>
+        <v>1.751857089968651</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.0293230190965546</v>
+        <v>0.1276476302589928</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1442</v>
+        <v>1568</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>529.4925264116406</v>
+        <v>547.2071697627046</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>28.75</v>
+        <v>31.1</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>61.65278410212029</v>
+        <v>35.13830303620269</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>21.96653259930564</v>
+        <v>22.8002054876211</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.9678740158893836</v>
+        <v>2.519628663635899</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.1069791151420884</v>
+        <v>-1.203468713761227</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1536</v>
+        <v>1531</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>高林股</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>527.8643268670584</v>
+        <v>542.1971516837867</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>53.2</v>
+        <v>13</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>55.73352970509677</v>
+        <v>54.65174099939487</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>17.16721029357413</v>
+        <v>20.13290913310757</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.386432686705837</v>
+        <v>0.7468886081133818</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.6861196158566328</v>
+        <v>0.0008761553814446</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1313</v>
+        <v>1527</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>鑽全</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>517.6597597605443</v>
+        <v>532.3415729757384</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>12.3</v>
+        <v>33.95</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>51.12116367938871</v>
+        <v>58.64366926449721</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>37.04147042252883</v>
+        <v>21.16061625223304</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4794538093240296</v>
+        <v>1.281909330394413</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.0574578997121486</v>
+        <v>0.0293230190965546</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1414</v>
+        <v>1442</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>516.3866821396109</v>
+        <v>529.4925264116406</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>18.75</v>
+        <v>28.75</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>59.63591630829549</v>
+        <v>61.65278410212029</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>29.29939917510715</v>
+        <v>21.96653259930564</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.315213000118487</v>
+        <v>0.9678740158893836</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.0001590327290805</v>
+        <v>0.1069791151420884</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1110</v>
+        <v>1536</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>東泥</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>516.2837615665295</v>
+        <v>527.8643268670584</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>15.75</v>
+        <v>53.2</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>55.2911037320906</v>
+        <v>55.73352970509677</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>31.55697785227025</v>
+        <v>17.16721029357413</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.9369801696824944</v>
+        <v>1.386432686705837</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.0033876252675852</v>
+        <v>0.6861196158566328</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1227</v>
+        <v>1313</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>512.5938569922181</v>
+        <v>517.6597597605443</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>29.85</v>
+        <v>12.3</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>56.68076291613404</v>
+        <v>51.12116367938871</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>25.29413413060842</v>
+        <v>37.04147042252883</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.976665813188127</v>
+        <v>0.4794538093240296</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.0466883247542116</v>
+        <v>-0.0574578997121486</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1418</v>
+        <v>1414</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>497.5791890149808</v>
+        <v>516.3866821396109</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>18.65</v>
+        <v>18.75</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>53.92761464201031</v>
+        <v>59.63591630829549</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>22.82794307461125</v>
+        <v>29.29939917510715</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.057918901498077</v>
+        <v>1.315213000118487</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.0831308506951817</v>
+        <v>-0.0001590327290805</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1312</v>
+        <v>1110</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>481.8621877564784</v>
+        <v>516.2837615665295</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>13.1</v>
+        <v>15.75</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>45.41466639435968</v>
+        <v>55.2911037320906</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>28.78952573425192</v>
+        <v>31.55697785227025</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.7944735458157831</v>
+        <v>0.9369801696824944</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.1769078867070907</v>
+        <v>-0.0033876252675852</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1455</v>
+        <v>1227</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>477.8754504758944</v>
+        <v>512.5938569922181</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>9.1</v>
+        <v>29.85</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>42.01709666158869</v>
+        <v>56.68076291613404</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>35.91512955434143</v>
+        <v>25.29413413060842</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.487545047589442</v>
+        <v>0.976665813188127</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.1547797971488134</v>
+        <v>0.0466883247542116</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1310</v>
+        <v>1418</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>476.9157685216347</v>
+        <v>497.5791890149808</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>10.3</v>
+        <v>18.65</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>53.94253720950768</v>
+        <v>53.92761464201031</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>35.01781760883906</v>
+        <v>22.82794307461125</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.5217812384514608</v>
+        <v>1.057918901498077</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.0322066121483097</v>
+        <v>0.0831308506951817</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1563</v>
+        <v>1312</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>巧新</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>474.2021663000479</v>
+        <v>481.8621877564784</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>64.5</v>
+        <v>13.1</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>51.28603471511142</v>
+        <v>45.41466639435968</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>35.86628615970904</v>
+        <v>28.78952573425192</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.6776778946345511</v>
+        <v>0.7944735458157831</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.6343847068021904</v>
+        <v>-0.1769078867070907</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1517</v>
+        <v>1455</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>利奇</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>463.8234032029745</v>
+        <v>477.8754504758944</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>10.75</v>
+        <v>9.1</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>53.45964751309902</v>
+        <v>42.01709666158869</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>22.85655068070804</v>
+        <v>35.91512955434143</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.338500611293231</v>
+        <v>0.487545047589442</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.0004123509797075</v>
+        <v>-0.1547797971488134</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>456.3072497492856</v>
+        <v>476.9157685216347</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>8.74</v>
+        <v>10.3</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>53.41241888838806</v>
+        <v>53.94253720950768</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>36.84661837111016</v>
+        <v>35.01781760883906</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.8097042829495062</v>
+        <v>0.5217812384514608</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.0047306879990734</v>
+        <v>-0.0322066121483097</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1514</v>
+        <v>1563</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>巧新</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>454.5258869075549</v>
+        <v>474.2021663000479</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>109.5</v>
+        <v>64.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>36.20695870130331</v>
+        <v>51.28603471511142</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>15.58953751480636</v>
+        <v>35.86628615970904</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>3.008710578677288</v>
+        <v>0.6776778946345511</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-1.088422747396402</v>
+        <v>-0.6343847068021904</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1464</v>
+        <v>1517</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>利奇</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>452.571409434059</v>
+        <v>463.8234032029745</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>10.55</v>
+        <v>10.75</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>51.50486579246138</v>
+        <v>53.45964751309902</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>24.35926286989869</v>
+        <v>22.85655068070804</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.6295279397979511</v>
+        <v>1.338500611293231</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.0036819343786264</v>
+        <v>0.0004123509797075</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1476</v>
+        <v>1314</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>445.6916137342924</v>
+        <v>456.3072497492856</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>343.5</v>
+        <v>8.74</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>57.64748259018851</v>
+        <v>53.41241888838806</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>19.75116280796942</v>
+        <v>36.84661837111016</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.7066711851716099</v>
+        <v>0.8097042829495062</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>3.248843100710065</v>
+        <v>-0.0047306879990734</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1467</v>
+        <v>1514</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>441.2759635735907</v>
+        <v>454.5258869075549</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>8.49</v>
+        <v>109.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>58.34438778790892</v>
+        <v>36.20695870130331</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>23.58304912952313</v>
+        <v>15.58953751480636</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.8126168541130432</v>
+        <v>3.008710578677288</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.0441503679281591</v>
+        <v>-1.088422747396402</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1440</v>
+        <v>1464</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>得力</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>440.8879366421058</v>
+        <v>452.571409434059</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>13.25</v>
+        <v>10.55</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>47.20266993905059</v>
+        <v>51.50486579246138</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>21.68854263803484</v>
+        <v>24.35926286989869</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.5400978443704991</v>
+        <v>0.6295279397979511</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.0690635965988438</v>
+        <v>0.0036819343786264</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1463</v>
+        <v>1476</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>437.0853000828326</v>
+        <v>445.6916137342924</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>17.45</v>
+        <v>343.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>42.38100362126252</v>
+        <v>57.64748259018851</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>25.01941551342556</v>
+        <v>19.75116280796942</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.6490774246188408</v>
+        <v>0.7066711851716099</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0289055924360078</v>
+        <v>3.248843100710065</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1308</v>
+        <v>1467</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>435.5253192347127</v>
+        <v>441.2759635735907</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>14.55</v>
+        <v>8.49</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>52.63807016573642</v>
+        <v>58.34438778790892</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>25.69967397773642</v>
+        <v>23.58304912952313</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.8149590192267459</v>
+        <v>0.8126168541130432</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.0384180508935139</v>
+        <v>0.0441503679281591</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1338</v>
+        <v>1440</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>430.6970768744888</v>
+        <v>440.8879366421058</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>16.25</v>
+        <v>13.25</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>41.8555547779841</v>
+        <v>47.20266993905059</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>18.87243991029925</v>
+        <v>21.68854263803484</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.920132906963144</v>
+        <v>0.5400978443704991</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.1117886048101891</v>
+        <v>-0.0690635965988438</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1582</v>
+        <v>1463</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>強盛新</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>430.5790535449842</v>
+        <v>437.0853000828326</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>76.2</v>
+        <v>17.45</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>29.98475577627576</v>
+        <v>42.38100362126252</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>25.41994694146094</v>
+        <v>25.01941551342556</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.8756550499193408</v>
+        <v>0.6490774246188408</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.344983826707911</v>
+        <v>0.0289055924360078</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1525</v>
+        <v>1308</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>江申</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>429.2725052816927</v>
+        <v>435.5253192347127</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>65.90000000000001</v>
+        <v>14.55</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>49.57328673423969</v>
+        <v>52.63807016573642</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>31.51400095925032</v>
+        <v>25.69967397773642</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.5321071378262532</v>
+        <v>0.8149590192267459</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.01725550462693</v>
+        <v>0.0384180508935139</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1558</v>
+        <v>1338</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>伸興</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>425.2039322917681</v>
+        <v>430.6970768744888</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>92.3</v>
+        <v>16.25</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>58.51893519131571</v>
+        <v>41.8555547779841</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>15.3722111645696</v>
+        <v>18.87243991029925</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.604093380236649</v>
+        <v>1.920132906963144</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.188417853548277</v>
+        <v>-0.1117886048101891</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1402</v>
+        <v>1582</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>422.99474531984</v>
+        <v>430.5790535449842</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>26.35</v>
+        <v>76.2</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>37.1118956398412</v>
+        <v>29.98475577627576</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>17.57915586122556</v>
+        <v>25.41994694146094</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.589151302847896</v>
+        <v>0.8756550499193408</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.3157185017052114</v>
+        <v>-0.344983826707911</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1339</v>
+        <v>1525</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>江申</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>421.7484727032884</v>
+        <v>429.2725052816927</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>44.2</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>51.51693694451971</v>
+        <v>49.57328673423969</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>21.01371625799492</v>
+        <v>31.51400095925032</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.8793861495294485</v>
+        <v>0.5321071378262532</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.0550426189548943</v>
+        <v>-0.01725550462693</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1309</v>
+        <v>1558</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>伸興</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>417.3570372902797</v>
+        <v>425.2039322917681</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>15</v>
+        <v>92.3</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>47.98392413473974</v>
+        <v>58.51893519131571</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>11.54701091917385</v>
+        <v>15.3722111645696</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.71173037566843</v>
+        <v>1.604093380236649</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.0780957764218719</v>
+        <v>0.188417853548277</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1460</v>
+        <v>1402</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>宏遠</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>407.2011033079064</v>
+        <v>422.99474531984</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>7</v>
+        <v>26.35</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>43.91288457143672</v>
+        <v>37.1118956398412</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>22.1499701915941</v>
+        <v>17.57915586122556</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.5719176408380569</v>
+        <v>1.589151302847896</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.0536263210560464</v>
+        <v>-0.3157185017052114</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1437</v>
+        <v>1339</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>392.4769717290116</v>
+        <v>421.7484727032884</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>30.45</v>
+        <v>44.2</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>56.39289289597432</v>
+        <v>51.51693694451971</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>25.33288834651372</v>
+        <v>21.01371625799492</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.307186838630202</v>
+        <v>0.8793861495294485</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.0080770136802125</v>
+        <v>-0.0550426189548943</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1528</v>
+        <v>1309</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>380.5871305829156</v>
+        <v>417.3570372902797</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>21.75</v>
+        <v>15</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>31.94608510096009</v>
+        <v>47.98392413473974</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>13.14180798364374</v>
+        <v>11.54701091917385</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.8590237987076791</v>
+        <v>1.71173037566843</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.1484377932551687</v>
+        <v>0.0780957764218719</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1477</v>
+        <v>1460</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>宏遠</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>376.6473636025989</v>
+        <v>407.2011033079064</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>220</v>
+        <v>7</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>47.20989018300217</v>
+        <v>43.91288457143672</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>15.28173772971384</v>
+        <v>22.1499701915941</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.5685585245624749</v>
+        <v>0.5719176408380569</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.1276738834710893</v>
+        <v>-0.0536263210560464</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1472</v>
+        <v>1437</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>370.6906694365557</v>
+        <v>392.4769717290116</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>86.90000000000001</v>
+        <v>30.45</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>46.44098521839286</v>
+        <v>56.39289289597432</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>12.36953069755585</v>
+        <v>25.33288834651372</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.1309906418626111</v>
+        <v>1.307186838630202</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.2751910203423303</v>
+        <v>-0.0080770136802125</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1201</v>
+        <v>1528</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>370.0240469791594</v>
+        <v>380.5871305829156</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>12.55</v>
+        <v>21.75</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>54.23837662425176</v>
+        <v>31.94608510096009</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>16.8055682289482</v>
+        <v>13.14180798364374</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.607011882136398</v>
+        <v>0.8590237987076791</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0173238397024309</v>
+        <v>-0.1484377932551687</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1516</v>
+        <v>1477</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>川飛</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>365.5753201304166</v>
+        <v>376.6473636025989</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>17.5</v>
+        <v>220</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>25.00543995290457</v>
+        <v>47.20989018300217</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>43.19858800189122</v>
+        <v>15.28173772971384</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.4960394318254605</v>
+        <v>0.5685585245624749</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.1441895998738243</v>
+        <v>0.1276738834710893</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1560</v>
+        <v>1472</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>359.9638650542139</v>
+        <v>370.6906694365557</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>675</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>44.22399162114282</v>
+        <v>46.44098521839286</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>18.1436350568745</v>
+        <v>12.36953069755585</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.8335796194910016</v>
+        <v>0.1309906418626111</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-9.41614835536314</v>
+        <v>-0.2751910203423303</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1305</v>
+        <v>1201</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>359.5666436694969</v>
+        <v>370.0240469791594</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>12.7</v>
+        <v>12.55</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>44.82754927591999</v>
+        <v>54.23837662425176</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>11.86599858500038</v>
+        <v>16.8055682289482</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.099081794491472</v>
+        <v>1.607011882136398</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.0610014616868266</v>
+        <v>0.0173238397024309</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1416</v>
+        <v>1516</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>川飛</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>359.1692150771565</v>
+        <v>365.5753201304166</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>11.2</v>
+        <v>17.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>54.79993478183422</v>
+        <v>25.00543995290457</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>16.4614286527288</v>
+        <v>43.19858800189122</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.455680629249606</v>
+        <v>0.4960394318254605</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0316632789311953</v>
+        <v>-0.1441895998738243</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1229</v>
+        <v>1560</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>357.4617685023865</v>
+        <v>359.9638650542139</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>40</v>
+        <v>675</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>37.65984990269298</v>
+        <v>44.22399162114282</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>23.66488632502937</v>
+        <v>18.1436350568745</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.7990601480044816</v>
+        <v>0.8335796194910016</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.3726599455105921</v>
+        <v>-9.41614835536314</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1256</v>
+        <v>1305</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>357.0902091007617</v>
+        <v>359.5666436694969</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>186</v>
+        <v>12.7</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>49.10506557661731</v>
+        <v>44.82754927591999</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>20.11415776582893</v>
+        <v>11.86599858500038</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.7026571673968993</v>
+        <v>1.099081794491472</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.7081612438597462</v>
+        <v>-0.0610014616868266</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1470</v>
+        <v>1416</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>大統新創</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>356.0390794179884</v>
+        <v>359.1692150771565</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>21.5</v>
+        <v>11.2</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>51.78086349849928</v>
+        <v>54.79993478183422</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>6.860197396611849</v>
+        <v>16.4614286527288</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.4311994351287399</v>
+        <v>1.455680629249606</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.4459318378820622</v>
+        <v>0.0316632789311953</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1321</v>
+        <v>1229</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>352.4362277248568</v>
+        <v>357.4617685023865</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>31.2</v>
+        <v>40</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>52.02286128646087</v>
+        <v>37.65984990269298</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>26.60961426929841</v>
+        <v>23.66488632502937</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.811256441209158</v>
+        <v>0.7990601480044816</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.047998201594009</v>
+        <v>-0.3726599455105921</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1217</v>
+        <v>1256</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>349.559822805291</v>
+        <v>357.0902091007617</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>9.9</v>
+        <v>186</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>49.29629823411431</v>
+        <v>49.10506557661731</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>18.59080286380517</v>
+        <v>20.11415776582893</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.06779301507388</v>
+        <v>0.7026571673968993</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.0003976556507556</v>
+        <v>0.7081612438597462</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1319</v>
+        <v>1470</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>大統新創</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>344.654849674251</v>
+        <v>356.0390794179884</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>75.40000000000001</v>
+        <v>21.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>36.96947926199267</v>
+        <v>51.78086349849928</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>29.61670896989087</v>
+        <v>6.860197396611849</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4168611944096609</v>
+        <v>0.4311994351287399</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.6305504283201437</v>
+        <v>0.4459318378820622</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1445</v>
+        <v>1321</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>大宇</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>342.5913625743294</v>
+        <v>352.4362277248568</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>11.45</v>
+        <v>31.2</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>48.91765819930393</v>
+        <v>52.02286128646087</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>28.46018969847018</v>
+        <v>26.60961426929841</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.346388922737505</v>
+        <v>0.811256441209158</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.0280807285525965</v>
+        <v>-0.047998201594009</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3972,21 +3972,21 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1513</v>
+        <v>1217</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>340.4542062759197</v>
+        <v>349.559822805291</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>164</v>
+        <v>9.9</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>38.57923772298226</v>
+        <v>49.29629823411431</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>15.90708551029143</v>
+        <v>18.59080286380517</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.5493552351961484</v>
+        <v>1.06779301507388</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-2.078520289194928</v>
+        <v>0.0003976556507556</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1446</v>
+        <v>1319</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>338.3998936745319</v>
+        <v>344.654849674251</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>14.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>25.88306487788199</v>
+        <v>36.96947926199267</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>30.41253819448215</v>
+        <v>29.61670896989087</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.739989367453191</v>
+        <v>0.4168611944096609</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.3247588396211786</v>
+        <v>-0.6305504283201437</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1413</v>
+        <v>1445</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>338.2892674970085</v>
+        <v>342.5913625743294</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>9.359999999999999</v>
+        <v>11.45</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>47.73355439772206</v>
+        <v>48.91765819930393</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>23.34434714858753</v>
+        <v>28.46018969847018</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.6080201932178434</v>
+        <v>0.346388922737505</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,7 +4121,7 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.0013580699898184</v>
+        <v>0.0280807285525965</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4131,21 +4131,21 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1503</v>
+        <v>1513</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>337.3531583796071</v>
+        <v>340.4542062759197</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>205</v>
+        <v>164</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>34.84802127252578</v>
+        <v>38.57923772298226</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>17.11511520562231</v>
+        <v>15.90708551029143</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.951326931326104</v>
+        <v>0.5493552351961484</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-4.435778441316424</v>
+        <v>-2.078520289194928</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1102</v>
+        <v>1446</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>336.651728867128</v>
+        <v>338.3998936745319</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>34.2</v>
+        <v>14.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>38.82310839073919</v>
+        <v>25.88306487788199</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>19.03287142466015</v>
+        <v>30.41253819448215</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.162370318587659</v>
+        <v>0.739989367453191</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.1831293742861862</v>
+        <v>-0.3247588396211786</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1236</v>
+        <v>1413</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>335.653425346957</v>
+        <v>338.2892674970085</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>22.95</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>23.21935582425061</v>
+        <v>47.73355439772206</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>15.77880933492189</v>
+        <v>23.34434714858753</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.972094405262528</v>
+        <v>0.6080201932178434</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.3072579693637481</v>
+        <v>-0.0013580699898184</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1108</v>
+        <v>1503</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>335.371062191132</v>
+        <v>337.3531583796071</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>13.5</v>
+        <v>205</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>37.95632775724113</v>
+        <v>34.84802127252578</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>21.57741181072052</v>
+        <v>17.11511520562231</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.86996078692004</v>
+        <v>0.951326931326104</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0170644998904973</v>
+        <v>-4.435778441316424</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1532</v>
+        <v>1102</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>334.7602680122641</v>
+        <v>336.651728867128</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>22.65</v>
+        <v>34.2</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>47.70427071768808</v>
+        <v>38.82310839073919</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>25.35309039293135</v>
+        <v>19.03287142466015</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.7794238763824614</v>
+        <v>1.162370318587659</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.1127328194079908</v>
+        <v>-0.1831293742861862</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1533</v>
+        <v>1236</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>328.3448128095732</v>
+        <v>335.653425346957</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>34.5</v>
+        <v>22.95</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>37.5379500247552</v>
+        <v>23.21935582425061</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>24.08485522367926</v>
+        <v>15.77880933492189</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.240518747273569</v>
+        <v>0.972094405262528</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.2157898680187737</v>
+        <v>-0.3072579693637481</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1454</v>
+        <v>1108</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>台富</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>325.6844257071082</v>
+        <v>335.371062191132</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>12.7</v>
+        <v>13.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>44.64398677420728</v>
+        <v>37.95632775724113</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>11.67334357630915</v>
+        <v>21.57741181072052</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.085669860442241</v>
+        <v>1.86996078692004</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.009831919603044499</v>
+        <v>-0.0170644998904973</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1324</v>
+        <v>1532</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>318.1735072964437</v>
+        <v>334.7602680122641</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>10.35</v>
+        <v>22.65</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>45.15668491361393</v>
+        <v>47.70427071768808</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>21.91288551340513</v>
+        <v>25.35309039293135</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.5792623645364136</v>
+        <v>0.7794238763824614</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0109867645868597</v>
+        <v>-0.1127328194079908</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1410</v>
+        <v>1533</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>310.7793681060592</v>
+        <v>328.3448128095732</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>26.05</v>
+        <v>34.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>51.74963158579843</v>
+        <v>37.5379500247552</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>20.13690698202064</v>
+        <v>24.08485522367926</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.306411237067573</v>
+        <v>1.240518747273569</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.16885549535539</v>
+        <v>-0.2157898680187737</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1419</v>
+        <v>1454</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>台富</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>309.6226928160006</v>
+        <v>325.6844257071082</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>66</v>
+        <v>12.7</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>50.65325627990898</v>
+        <v>44.64398677420728</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>18.79122370523588</v>
+        <v>11.67334357630915</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.7373622721333466</v>
+        <v>1.085669860442241</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0336127913481963</v>
+        <v>-0.009831919603044499</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1233</v>
+        <v>1324</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>天仁</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>306.3870064277369</v>
+        <v>318.1735072964437</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>28.15</v>
+        <v>10.35</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>50.19465417349898</v>
+        <v>45.15668491361393</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>10.51717269880103</v>
+        <v>21.91288551340513</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.8675895654873352</v>
+        <v>0.5792623645364136</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0080493526854014</v>
+        <v>-0.0109867645868597</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1316</v>
+        <v>1410</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>南染</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>301.9441899733812</v>
+        <v>310.7793681060592</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>10.2</v>
+        <v>26.05</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>42.13274280773802</v>
+        <v>51.74963158579843</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>11.54432485853557</v>
+        <v>20.13690698202064</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.206250332408116</v>
+        <v>0.306411237067573</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.0159467466146498</v>
+        <v>0.16885549535539</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1218</v>
+        <v>1419</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>301.675639227368</v>
+        <v>309.6226928160006</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>15.14948673251602</v>
+        <v>50.65325627990898</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>45.94130278045908</v>
+        <v>18.79122370523588</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.567563922736797</v>
+        <v>0.7373622721333466</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.1461541482061645</v>
+        <v>-0.0336127913481963</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1474</v>
+        <v>1233</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>弘裕</t>
+          <t>天仁</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>300.9387119072897</v>
+        <v>306.3870064277369</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>10.4</v>
+        <v>28.15</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>51.58900041466439</v>
+        <v>50.19465417349898</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>35.66722791353672</v>
+        <v>10.51717269880103</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.6194243017375934</v>
+        <v>0.8675895654873352</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0016603746577754</v>
+        <v>0.0080493526854014</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1504</v>
+        <v>1316</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>300.0465818311126</v>
+        <v>301.9441899733812</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>63.6</v>
+        <v>10.2</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>37.23682777241916</v>
+        <v>42.13274280773802</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>12.2224881058369</v>
+        <v>11.54432485853557</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.9297562401260514</v>
+        <v>1.206250332408116</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.6164519989371565</v>
+        <v>-0.0159467466146498</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>293.444977458579</v>
+        <v>301.675639227368</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>113</v>
+        <v>16</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>39.76845247896123</v>
+        <v>15.14948673251602</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>45.80572614746136</v>
+        <v>45.94130278045908</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.8677235386979025</v>
+        <v>1.567563922736797</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.6808997620256925</v>
+        <v>-0.1461541482061645</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1451</v>
+        <v>1474</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>年興</t>
+          <t>弘裕</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>286.4202012920509</v>
+        <v>300.9387119072897</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>17.05</v>
+        <v>10.4</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>50.95862535814152</v>
+        <v>51.58900041466439</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>17.83145747911876</v>
+        <v>35.66722791353672</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.043503059143254</v>
+        <v>0.6194243017375934</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0076360798131796</v>
+        <v>-0.0016603746577754</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1323</v>
+        <v>1504</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>永裕</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>285.023538161628</v>
+        <v>300.0465818311126</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>19.95</v>
+        <v>63.6</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>48.71181658866129</v>
+        <v>37.23682777241916</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>17.32028591504001</v>
+        <v>12.2224881058369</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.135903380907166</v>
+        <v>0.9297562401260514</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0380997973058771</v>
+        <v>-0.6164519989371565</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1304</v>
+        <v>1215</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>280.7475805448244</v>
+        <v>293.444977458579</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>13.55</v>
+        <v>113</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>50.00388392695811</v>
+        <v>39.76845247896123</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>17.25152603069831</v>
+        <v>45.80572614746136</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.035458299601344</v>
+        <v>0.8677235386979025</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0345232864721903</v>
+        <v>0.6808997620256925</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1530</v>
+        <v>1451</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>年興</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>277.5342643832158</v>
+        <v>286.4202012920509</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>29.35</v>
+        <v>17.05</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>48.88620703314601</v>
+        <v>50.95862535814152</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>14.29853342701194</v>
+        <v>17.83145747911876</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.197791817279988</v>
+        <v>1.043503059143254</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0229566207898259</v>
+        <v>0.0076360798131796</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1423</v>
+        <v>1323</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>273.5483112469133</v>
+        <v>285.023538161628</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>36.7</v>
+        <v>19.95</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>31.32172496247979</v>
+        <v>48.71181658866129</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>34.61925154131173</v>
+        <v>17.32028591504001</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.4124298999722158</v>
+        <v>1.135903380907166</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0494586261468099</v>
+        <v>0.0380997973058771</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1521</v>
+        <v>1304</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>273.2672898039784</v>
+        <v>280.7475805448244</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>25.5</v>
+        <v>13.55</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>42.47830351428534</v>
+        <v>50.00388392695811</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>12.3730369240318</v>
+        <v>17.25152603069831</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.644984383837887</v>
+        <v>1.035458299601344</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.07253281028497589</v>
+        <v>-0.0345232864721903</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1438</v>
+        <v>1530</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>亞崴</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>272.0817015312459</v>
+        <v>277.5342643832158</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>21.4</v>
+        <v>29.35</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>42.89636615476</v>
+        <v>48.88620703314601</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>15.41855548401985</v>
+        <v>14.29853342701194</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.4847365028562895</v>
+        <v>1.197791817279988</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.1379299606024961</v>
+        <v>-0.0229566207898259</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1213</v>
+        <v>1423</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>268.5449003848608</v>
+        <v>273.5483112469133</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>7.48</v>
+        <v>36.7</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>48.56043593042248</v>
+        <v>31.32172496247979</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>4.778549767440754</v>
+        <v>34.61925154131173</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.1957822413111118</v>
+        <v>0.4124298999722158</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.008926325753640199</v>
+        <v>-0.0494586261468099</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1526</v>
+        <v>1521</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>日馳</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>267.2625231306144</v>
+        <v>273.2672898039784</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>14.2</v>
+        <v>25.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>42.15985708268528</v>
+        <v>42.47830351428534</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>18.87954861437479</v>
+        <v>12.3730369240318</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.17053259677354</v>
+        <v>0.644984383837887</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0157232263235757</v>
+        <v>-0.07253281028497589</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1219</v>
+        <v>1438</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>261.0011089816251</v>
+        <v>272.0817015312459</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>11.8</v>
+        <v>21.4</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>22.81357236024174</v>
+        <v>42.89636615476</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>37.38612724142224</v>
+        <v>15.41855548401985</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.466747543348486</v>
+        <v>0.4847365028562895</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0450218536667335</v>
+        <v>-0.1379299606024961</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1519</v>
+        <v>1213</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>254.9640118903873</v>
+        <v>268.5449003848608</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>692</v>
+        <v>7.48</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>30.02010275148031</v>
+        <v>48.56043593042248</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>17.88338207408911</v>
+        <v>4.778549767440754</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.541730192983283</v>
+        <v>0.1957822413111118</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-6.731066032934365</v>
+        <v>-0.008926325753640199</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1225</v>
+        <v>1526</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>日馳</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>249.4140885788271</v>
+        <v>267.2625231306144</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>26.5</v>
+        <v>14.2</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>30.08547690317562</v>
+        <v>42.15985708268528</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>25.14963095715305</v>
+        <v>18.87954861437479</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.3874868984231283</v>
+        <v>1.17053259677354</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.3063837438019366</v>
+        <v>0.0157232263235757</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>1524</v>
+        <v>1219</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>245.3206891742655</v>
+        <v>261.0011089816251</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>27.5</v>
+        <v>11.8</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>34.52319009711051</v>
+        <v>22.81357236024174</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>15.52716432194729</v>
+        <v>37.38612724142224</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.2788741138997</v>
+        <v>1.466747543348486</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.1556625469056832</v>
+        <v>-0.0450218536667335</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1443</v>
+        <v>1519</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>244.724196493844</v>
+        <v>254.9640118903873</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>26.15</v>
+        <v>692</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>47.41130306272238</v>
+        <v>30.02010275148031</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>14.98163577675044</v>
+        <v>17.88338207408911</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.9264449982015496</v>
+        <v>1.541730192983283</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.1092371129843428</v>
+        <v>-6.731066032934365</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1220</v>
+        <v>1225</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>235.5342297519121</v>
+        <v>249.4140885788271</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>11.45</v>
+        <v>26.5</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>36.169883790681</v>
+        <v>30.08547690317562</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>25.24875239611341</v>
+        <v>25.14963095715305</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.5514666545824852</v>
+        <v>0.3874868984231283</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.0060610405543805</v>
+        <v>-0.3063837438019366</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5774,21 +5774,21 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>1529</v>
+        <v>1524</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>232.4117243772916</v>
+        <v>245.3206891742655</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>21.05</v>
+        <v>27.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>37.84231831961154</v>
+        <v>34.52319009711051</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>13.37171630846276</v>
+        <v>15.52716432194729</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.408910359356287</v>
+        <v>1.2788741138997</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.1653933732018425</v>
+        <v>-0.1556625469056832</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5827,21 +5827,21 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>1537</v>
+        <v>1443</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>廣隆</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>226.7829798079545</v>
+        <v>244.724196493844</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>125.5</v>
+        <v>26.15</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>46.71435365509119</v>
+        <v>47.41130306272238</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>19.55800806570884</v>
+        <v>14.98163577675044</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>2.066380813655294</v>
+        <v>0.9264449982015496</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0606761314191188</v>
+        <v>-0.1092371129843428</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>1307</v>
+        <v>1220</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>226.5660875920734</v>
+        <v>235.5342297519121</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>32.5</v>
+        <v>11.45</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>40.89803899825048</v>
+        <v>36.169883790681</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>19.45777626796205</v>
+        <v>25.24875239611341</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.5267496585446629</v>
+        <v>0.5514666545824852</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.4297095680368752</v>
+        <v>-0.0060610405543805</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1439</v>
+        <v>1529</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>220.6184690842813</v>
+        <v>232.4117243772916</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>23.9</v>
+        <v>21.05</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>45.3907686620983</v>
+        <v>37.84231831961154</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>12.68057462393916</v>
+        <v>13.37171630846276</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.200938114692087</v>
+        <v>1.408910359356287</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0233871467992322</v>
+        <v>-0.1653933732018425</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1101</v>
+        <v>1537</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>廣隆</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>218.2633123593066</v>
+        <v>226.7829798079545</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>22.7</v>
+        <v>125.5</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>34.9489931786095</v>
+        <v>46.71435365509119</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>15.08025027275693</v>
+        <v>19.55800806570884</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.8435773861410759</v>
+        <v>2.066380813655294</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.1241024129469964</v>
+        <v>-0.0606761314191188</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1104</v>
+        <v>1307</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>215.274932676005</v>
+        <v>226.5660875920734</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>26.75</v>
+        <v>32.5</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>35.22473014793734</v>
+        <v>40.89803899825048</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>25.39548780310182</v>
+        <v>19.45777626796205</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.8960641135652202</v>
+        <v>0.5267496585446629</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0386457685861533</v>
+        <v>-0.4297095680368752</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1471</v>
+        <v>1439</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>214.7769164987856</v>
+        <v>220.6184690842813</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>10.05</v>
+        <v>23.9</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>38.3942297377543</v>
+        <v>45.3907686620983</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>10.62188024471757</v>
+        <v>12.68057462393916</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.055211311937096</v>
+        <v>1.200938114692087</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0702857370580095</v>
+        <v>0.0233871467992322</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>1475</v>
+        <v>1101</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>業旺</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>213.867113562016</v>
+        <v>218.2633123593066</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>26.85</v>
+        <v>22.7</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>47.36174976826332</v>
+        <v>34.9489931786095</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>18.34330254965484</v>
+        <v>15.08025027275693</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.5411781740133975</v>
+        <v>0.8435773861410759</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0485749915943199</v>
+        <v>-0.1241024129469964</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>1538</v>
+        <v>1104</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>環泥</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>207.4536833599214</v>
+        <v>215.274932676005</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>10.6</v>
+        <v>26.75</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>52.3177994367121</v>
+        <v>35.22473014793734</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>6.520506385399583</v>
+        <v>25.39548780310182</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.393240306418464</v>
+        <v>0.8960641135652202</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.5758345177643173</v>
+        <v>-0.0386457685861533</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1541</v>
+        <v>1471</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>錩泰</t>
+          <t>首利</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>207.2969405132846</v>
+        <v>214.7769164987856</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>21.6</v>
+        <v>10.05</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>49.73984936234446</v>
+        <v>38.3942297377543</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>10.99428376207039</v>
+        <v>10.62188024471757</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.767713330807636</v>
+        <v>1.055211311937096</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0272436074691792</v>
+        <v>-0.0702857370580095</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>1325</v>
+        <v>1475</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>恆大</t>
+          <t>業旺</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>196.2039628759556</v>
+        <v>213.867113562016</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>24.35</v>
+        <v>26.85</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>38.18491609505526</v>
+        <v>47.36174976826332</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>22.49094433665456</v>
+        <v>18.34330254965484</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.460426579665354</v>
+        <v>0.5411781740133975</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0075446502455384</v>
+        <v>-0.0485749915943199</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>1459</v>
+        <v>1538</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>194.3533006028242</v>
+        <v>207.4536833599214</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>11.6</v>
+        <v>10.6</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>44.27503331381376</v>
+        <v>52.3177994367121</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>15.5380729328355</v>
+        <v>6.520506385399583</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.5632506506657513</v>
+        <v>1.393240306418464</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0162556057498078</v>
+        <v>0.5758345177643173</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1457</v>
+        <v>1541</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>宜進</t>
+          <t>錩泰</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>192.7434885018445</v>
+        <v>207.2969405132846</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>14.1</v>
+        <v>21.6</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>43.71186835783876</v>
+        <v>49.73984936234446</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>12.72194949273432</v>
+        <v>10.99428376207039</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.6032445070409376</v>
+        <v>1.767713330807636</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0118257430738177</v>
+        <v>0.0272436074691792</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>1535</v>
+        <v>1325</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>中宇</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>189.447547252281</v>
+        <v>196.2039628759556</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>49.9</v>
+        <v>24.35</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>48.12463188804901</v>
+        <v>38.18491609505526</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>29.19947829815031</v>
+        <v>22.49094433665456</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.484488816250766</v>
+        <v>1.460426579665354</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0001752900312801</v>
+        <v>-0.0075446502455384</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,21 +6516,21 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>1569</v>
+        <v>1459</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>185.6004269568014</v>
+        <v>194.3533006028242</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>47.4</v>
+        <v>11.6</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>45.72901941032121</v>
+        <v>44.27503331381376</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>13.74208081132924</v>
+        <v>15.5380729328355</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.156556008564884</v>
+        <v>0.5632506506657513</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.3152445397821506</v>
+        <v>-0.0162556057498078</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>1473</v>
+        <v>1457</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>宜進</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>176.4641043829956</v>
+        <v>192.7434885018445</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>20.2</v>
+        <v>14.1</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>45.28907958621578</v>
+        <v>43.71186835783876</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>17.75397514906109</v>
+        <v>12.72194949273432</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.914563803813788</v>
+        <v>0.6032445070409376</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0440308291455153</v>
+        <v>-0.0118257430738177</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>1441</v>
+        <v>1535</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>中宇</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>172.8009250903986</v>
+        <v>189.447547252281</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>9.1</v>
+        <v>49.9</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>43.23113328928488</v>
+        <v>48.12463188804901</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>24.36376669908979</v>
+        <v>29.19947829815031</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.039335536333633</v>
+        <v>1.484488816250766</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.0222097254276815</v>
+        <v>-0.0001752900312801</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6675,21 +6675,21 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>1436</v>
+        <v>1569</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>165.4342510173308</v>
+        <v>185.6004269568014</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>44.45</v>
+        <v>47.4</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>39.14434176544673</v>
+        <v>45.72901941032121</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>13.33486112356562</v>
+        <v>13.74208081132924</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.7664966861510981</v>
+        <v>1.156556008564884</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0125144323404243</v>
+        <v>0.3152445397821506</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6728,21 +6728,21 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>1432</v>
+        <v>1473</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>165.3917082530021</v>
+        <v>176.4641043829956</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>15.15</v>
+        <v>20.2</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>32.12541041537082</v>
+        <v>45.28907958621578</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>32.06201888542777</v>
+        <v>17.75397514906109</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.4744466888639313</v>
+        <v>0.914563803813788</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0328132963197569</v>
+        <v>0.0440308291455153</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>1522</v>
+        <v>1441</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>161.2551147805592</v>
+        <v>172.8009250903986</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>29.85</v>
+        <v>9.1</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>43.06089803738281</v>
+        <v>43.23113328928488</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>10.96719700164518</v>
+        <v>24.36376669908979</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>1.457766307289311</v>
+        <v>1.039335536333633</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.016814847098063</v>
+        <v>0.0222097254276815</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>1512</v>
+        <v>1436</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>瑞利</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>158.1956690098357</v>
+        <v>165.4342510173308</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>6.75</v>
+        <v>44.45</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>42.58540388970175</v>
+        <v>39.14434176544673</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>13.1391145003716</v>
+        <v>13.33486112356562</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.929135256488853</v>
+        <v>0.7664966861510981</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.0032652536153046</v>
+        <v>0.0125144323404243</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6887,21 +6887,21 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>1231</v>
+        <v>1432</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>156.8264710815479</v>
+        <v>165.3917082530021</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>85.8</v>
+        <v>15.15</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>41.61249723193741</v>
+        <v>32.12541041537082</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>14.5748845119515</v>
+        <v>32.06201888542777</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.193953073010108</v>
+        <v>0.4744466888639313</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.2443530460667102</v>
+        <v>-0.0328132963197569</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>1453</v>
+        <v>1522</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>144.7708500062851</v>
+        <v>161.2551147805592</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>11.1</v>
+        <v>29.85</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>40.71770654561888</v>
+        <v>43.06089803738281</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>18.47475770261717</v>
+        <v>10.96719700164518</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>1.393402115921858</v>
+        <v>1.457766307289311</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.0297766918798049</v>
+        <v>-0.016814847098063</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>1340</v>
+        <v>1512</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>瑞利</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>138.6836579495207</v>
+        <v>158.1956690098357</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>5.29</v>
+        <v>6.75</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>39.97574677940754</v>
+        <v>42.58540388970175</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>16.28043353528283</v>
+        <v>13.1391145003716</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.8809303262142214</v>
+        <v>0.929135256488853</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.0086279220118867</v>
+        <v>0.0032652536153046</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,21 +7046,21 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>1417</v>
+        <v>1231</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>136.9665545473901</v>
+        <v>156.8264710815479</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>8.630000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>48.57708547789438</v>
+        <v>41.61249723193741</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>18.3068745732826</v>
+        <v>14.5748845119515</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.9011718441909332</v>
+        <v>1.193953073010108</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.0024565112884513</v>
+        <v>-0.2443530460667102</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>1456</v>
+        <v>1453</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>132.2546984690731</v>
+        <v>144.7708500062851</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>13.75</v>
+        <v>11.1</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>45.33152474104494</v>
+        <v>40.71770654561888</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>18.22521138447382</v>
+        <v>18.47475770261717</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>1.050605356971972</v>
+        <v>1.393402115921858</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.1215483921205902</v>
+        <v>-0.0297766918798049</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>1103</v>
+        <v>1340</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>124.6062334380677</v>
+        <v>138.6836579495207</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>13.4</v>
+        <v>5.29</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>46.5192029141136</v>
+        <v>39.97574677940754</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>10.90998098938309</v>
+        <v>16.28043353528283</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>1.427267555717348</v>
+        <v>0.8809303262142214</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.0187893952978749</v>
+        <v>-0.0086279220118867</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>1341</v>
+        <v>1417</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>120.9636796310094</v>
+        <v>136.9665545473901</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>59</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>51.64535790841678</v>
+        <v>48.57708547789438</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>18.94509725744501</v>
+        <v>18.3068745732826</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.1247793453800649</v>
+        <v>0.9011718441909332</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-1.201709373104885</v>
+        <v>0.0024565112884513</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>1109</v>
+        <v>1456</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>102.421925687396</v>
+        <v>132.2546984690731</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>14.55</v>
+        <v>13.75</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>42.8008278259677</v>
+        <v>45.33152474104494</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>14.3207190611819</v>
+        <v>18.22521138447382</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>1.180666558508049</v>
+        <v>1.050605356971972</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7301,62 +7301,221 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.0156720354846428</v>
+        <v>-0.1215483921205902</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>嘉泥</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>124.6062334380677</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>46.5192029141136</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>10.90998098938309</v>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>1.427267555717348</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N130" s="2" t="n">
+        <v>-0.0187893952978749</v>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>1341</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>富林-KY</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>120.9636796310094</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>51.64535790841678</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>18.94509725744501</v>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>0.1247793453800649</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N131" s="2" t="n">
+        <v>-1.201709373104885</v>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, williams_r_recovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>信大</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>102.421925687396</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>42.8008278259677</v>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>14.3207190611819</v>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>1.180666558508049</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N132" s="2" t="n">
+        <v>0.0156720354846428</v>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
         <v>1539</v>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>巨庭</t>
         </is>
       </c>
-      <c r="C130" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D130" s="2" t="n">
+      <c r="C133" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D133" s="2" t="n">
         <v>82.23385222724006</v>
       </c>
-      <c r="E130" s="2" t="n">
+      <c r="E133" s="2" t="n">
         <v>15.65</v>
       </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H130" s="2" t="n">
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H133" s="2" t="n">
         <v>44.83996258937296</v>
       </c>
-      <c r="I130" s="2" t="n">
+      <c r="I133" s="2" t="n">
         <v>12.82630296779307</v>
       </c>
-      <c r="J130" s="2" t="n">
+      <c r="J133" s="2" t="n">
         <v>0.8347430802648043</v>
       </c>
-      <c r="K130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M130" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N130" s="2" t="n">
+      <c r="K133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N133" s="2" t="n">
         <v>0.0046782553539784</v>
       </c>
-      <c r="O130" s="2" t="inlineStr">
+      <c r="O133" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
